--- a/public/templates/bom_import_template.xlsx
+++ b/public/templates/bom_import_template.xlsx
@@ -397,86 +397,295 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:Q5"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" customWidth="1"/>
+    <col min="9" max="9" width="10.83203125" customWidth="1"/>
+    <col min="10" max="10" width="10.83203125" customWidth="1"/>
+    <col min="11" max="11" width="10.83203125" customWidth="1"/>
+    <col min="12" max="12" width="10.83203125" customWidth="1"/>
+    <col min="13" max="13" width="10.83203125" customWidth="1"/>
+    <col min="14" max="14" width="10.83203125" customWidth="1"/>
+    <col min="15" max="15" width="10.83203125" customWidth="1"/>
+    <col min="16" max="16" width="10.83203125" customWidth="1"/>
+    <col min="17" max="17" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>母件料号</v>
+        <v>BOM单号</v>
       </c>
       <c r="B1" t="str">
-        <v>子件料号</v>
+        <v>顺序号</v>
       </c>
       <c r="C1" t="str">
-        <v>规格</v>
+        <v>物料代码</v>
       </c>
       <c r="D1" t="str">
-        <v>数量</v>
+        <v>物料名称</v>
       </c>
       <c r="E1" t="str">
+        <v>规格型号</v>
+      </c>
+      <c r="F1" t="str">
+        <v>物料类型</v>
+      </c>
+      <c r="G1" t="str">
+        <v>辅助属性</v>
+      </c>
+      <c r="H1" t="str">
+        <v>基本单位</v>
+      </c>
+      <c r="I1" t="str">
+        <v>基本用量</v>
+      </c>
+      <c r="J1" t="str">
+        <v>单位</v>
+      </c>
+      <c r="K1" t="str">
+        <v>用量</v>
+      </c>
+      <c r="L1" t="str">
+        <v>费用</v>
+      </c>
+      <c r="M1" t="str">
+        <v>损耗率</v>
+      </c>
+      <c r="N1" t="str">
+        <v>使用状态</v>
+      </c>
+      <c r="O1" t="str">
+        <v>发料仓库</v>
+      </c>
+      <c r="P1" t="str">
         <v>备注</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>审核状态</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>BOM-2026-001</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2" t="str">
         <v>M-100</v>
       </c>
-      <c r="B2" t="str">
-        <v>C-A</v>
-      </c>
-      <c r="C2" t="str">
-        <v>1000mm</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
+      <c r="D2" t="str">
+        <v>成品总成A</v>
       </c>
       <c r="E2" t="str">
-        <v>示例：同料号可不同规格</v>
+        <v>标准版</v>
+      </c>
+      <c r="F2" t="str">
+        <v>母件</v>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v>套</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2" t="str">
+        <v>套</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="str">
+        <v>启用</v>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v>母件行：填写母件完整信息</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>已审核</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>M-100</v>
-      </c>
-      <c r="B3" t="str">
+        <v>BOM-2026-001</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="str">
         <v>C-A</v>
       </c>
-      <c r="C3" t="str">
-        <v>800mm</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
+      <c r="D3" t="str">
+        <v>配件管件</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>1000mm</v>
+      </c>
+      <c r="F3" t="str">
+        <v>子件</v>
+      </c>
+      <c r="G3" t="str">
+        <v>镀锌</v>
+      </c>
+      <c r="H3" t="str">
+        <v>根</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3" t="str">
+        <v>根</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="str">
+        <v>启用</v>
+      </c>
+      <c r="O3" t="str">
+        <v>原料仓</v>
+      </c>
+      <c r="P3" t="str">
+        <v>同料号不同规格可分行</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>已审核</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>M-100</v>
-      </c>
-      <c r="B4" t="str">
+        <v>BOM-2026-001</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4" t="str">
+        <v>C-A</v>
+      </c>
+      <c r="D4" t="str">
+        <v>配件管件</v>
+      </c>
+      <c r="E4" t="str">
+        <v>800mm</v>
+      </c>
+      <c r="F4" t="str">
+        <v>子件</v>
+      </c>
+      <c r="G4" t="str">
+        <v>镀锌</v>
+      </c>
+      <c r="H4" t="str">
+        <v>根</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4" t="str">
+        <v>根</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="str">
+        <v>启用</v>
+      </c>
+      <c r="O4" t="str">
+        <v>原料仓</v>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v>已审核</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>BOM-2026-001</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" t="str">
         <v>C-B</v>
       </c>
-      <c r="C4" t="str">
+      <c r="D5" t="str">
+        <v>连接件</v>
+      </c>
+      <c r="E5" t="str">
         <v>标准</v>
       </c>
-      <c r="D4">
+      <c r="F5" t="str">
+        <v>子件</v>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v>个</v>
+      </c>
+      <c r="I5">
         <v>3</v>
       </c>
-      <c r="E4" t="str">
-        <v>导入时自选母件列与母件值</v>
+      <c r="J5" t="str">
+        <v>个</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5">
+        <v>0.02</v>
+      </c>
+      <c r="N5" t="str">
+        <v>启用</v>
+      </c>
+      <c r="O5" t="str">
+        <v>原料仓</v>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
+        <v>已审核</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q5"/>
   </ignoredErrors>
 </worksheet>
 </file>